--- a/results/Int All Data 0.3/Rando_1_permute.xlsx
+++ b/results/Int All Data 0.3/Rando_1_permute.xlsx
@@ -440,1237 +440,1237 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.650481122232098</v>
+        <v>0.654733381546768</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6500788068831119</v>
+        <v>0.6541012702951877</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6495329553547275</v>
+        <v>0.6530958269616152</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6492168997289374</v>
+        <v>0.6530958269616152</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6492168997289374</v>
+        <v>0.6519178641816505</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6492168997289374</v>
+        <v>0.6519178641816505</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6486710482005531</v>
+        <v>0.6510559570274761</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6486710482005531</v>
+        <v>0.6526645283456352</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6510269737604822</v>
+        <v>0.6525782686224392</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6521476600842446</v>
+        <v>0.6541585467513898</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6442462694394913</v>
+        <v>0.6526645283456352</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6436141581879109</v>
+        <v>0.6536989549462016</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6470617868046087</v>
+        <v>0.6529233075152231</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6470617868046087</v>
+        <v>0.6520614003610488</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6485558052103633</v>
+        <v>0.6529233075152231</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6485558052103633</v>
+        <v>0.6478664175025809</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6491879164619436</v>
+        <v>0.6472343062510006</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6494177123645377</v>
+        <v>0.648786291190743</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6409697801136144</v>
+        <v>0.6461143100050237</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6358266303777762</v>
+        <v>0.6452524028508493</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6348784635004058</v>
+        <v>0.6489298273701412</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6341028160694273</v>
+        <v>0.6489298273701412</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6367175207989444</v>
+        <v>0.6475220686875824</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6367175207989444</v>
+        <v>0.6484702355649529</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6054328443902197</v>
+        <v>0.6489298273701412</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.604025085707661</v>
+        <v>0.6497917345243156</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.604025085707661</v>
+        <v>0.6497917345243156</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6056053638366117</v>
+        <v>0.6455684584766395</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.592302044286432</v>
+        <v>0.6497054748011196</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5948877657489552</v>
+        <v>0.6497054748011196</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5948877657489552</v>
+        <v>0.6481251966721688</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5943419142205709</v>
+        <v>0.6489871038263433</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5943419142205709</v>
+        <v>0.6486130816665654</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5939395988715848</v>
+        <v>0.6482970260407753</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5994843738786236</v>
+        <v>0.6482970260407753</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5990820585296375</v>
+        <v>0.6482970260407753</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5925891166452282</v>
+        <v>0.6486130816665654</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5945434169339567</v>
+        <v>0.6477511745123911</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5965832868680958</v>
+        <v>0.6480672301381811</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5958938991603133</v>
+        <v>0.6477511745123911</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.590262174352293</v>
+        <v>0.6501933597955162</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5893995771203331</v>
+        <v>0.6505094154213062</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5887674658687527</v>
+        <v>0.6507392113239004</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5887674658687527</v>
+        <v>0.6520034338270611</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5817279823781736</v>
+        <v>0.6520034338270611</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5817279823781736</v>
+        <v>0.6471763397170129</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5861527611392356</v>
+        <v>0.6466877646448308</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5868711321140119</v>
+        <v>0.6475206885320113</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5876757628119842</v>
+        <v>0.6478367441578015</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5835380564097186</v>
+        <v>0.6480665400603955</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5832220007839284</v>
+        <v>0.6505949850667168</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5902325010075136</v>
+        <v>0.6505949850667168</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5915250166998824</v>
+        <v>0.6499628738151364</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.587410772942326</v>
+        <v>0.6478940206140036</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5821233969493042</v>
+        <v>0.6449632602586963</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5673854056829286</v>
+        <v>0.6445609449097103</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5647707009534115</v>
+        <v>0.6451067964380945</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5647707009534115</v>
+        <v>0.6494453154759604</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5629875399555038</v>
+        <v>0.6499621837373509</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5624416884271195</v>
+        <v>0.645537404976289</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5658030573206212</v>
+        <v>0.6461695162278692</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5634761150276859</v>
+        <v>0.6478063807352364</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.562699777518922</v>
+        <v>0.6367734170995755</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5620676662673416</v>
+        <v>0.6401347859930772</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5572695554242875</v>
+        <v>0.6391866191157067</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5572695554242875</v>
+        <v>0.6354498479068561</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5572695554242875</v>
+        <v>0.6353918813728684</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5579016666758677</v>
+        <v>0.6353918813728684</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.554108999166386</v>
+        <v>0.6295593439292477</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5602003157795947</v>
+        <v>0.6234970105830329</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5569838632210623</v>
+        <v>0.6275194739951088</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5451752521544229</v>
+        <v>0.6154803769480895</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5449164729848348</v>
+        <v>0.6175202468822285</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5555188280823014</v>
+        <v>0.6333527015165149</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5475021944473581</v>
+        <v>0.6342146086706894</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5338248527374005</v>
+        <v>0.6342146086706894</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5282510944633679</v>
+        <v>0.6361675288038469</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5339670087612276</v>
+        <v>0.6361675288038469</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5323867306322768</v>
+        <v>0.6390693058921602</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5322135211080993</v>
+        <v>0.6376884602432387</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4630180413936259</v>
+        <v>0.6335797371079668</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.46324783729622</v>
+        <v>0.6282357747365283</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4459820911013089</v>
+        <v>0.6282357747365283</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4461539204699154</v>
+        <v>0.6295558935403198</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4550842170929507</v>
+        <v>0.6282916710371593</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4538206846675757</v>
+        <v>0.6144135166916015</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4501156570368612</v>
+        <v>0.6034944158905592</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.467063967450411</v>
+        <v>0.6016553585920205</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.467409006343195</v>
+        <v>0.5966557450355804</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.4773488867665163</v>
+        <v>0.5950464836396359</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.4818599252507743</v>
+        <v>0.6032349466431857</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.4877214459613888</v>
+        <v>0.6113951164575271</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.4860549081092421</v>
+        <v>0.6013958893446469</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.4741572770082644</v>
+        <v>0.6015684087910389</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.4824064668569441</v>
+        <v>0.5992124832311099</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.4802520440104009</v>
+        <v>0.5992124832311099</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.4762012874091167</v>
+        <v>0.5998445944826901</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.4752531205317463</v>
+        <v>0.6071428571428572</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.4502019167600572</v>
+        <v>0.6073153765892492</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.4512936198168257</v>
+        <v>0.6101308939543666</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.4538786512015635</v>
+        <v>0.6109651979971182</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.4592233036507875</v>
+        <v>0.5681507019471235</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.4722361004532431</v>
+        <v>0.5651626651356141</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.4712016738526766</v>
+        <v>0.5539882355539116</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.4634741828098863</v>
+        <v>0.5793016688841166</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.4634741828098863</v>
+        <v>0.5749638399240362</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.4547398682779523</v>
+        <v>0.5752798955498264</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.4444266557726387</v>
+        <v>0.5519235228194923</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.4420997134797034</v>
+        <v>0.5519235228194923</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.4451457168252005</v>
+        <v>0.555773466785176</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.4451457168252005</v>
+        <v>0.5088129833994888</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.4352023860129514</v>
+        <v>0.5025802008402387</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.4447427113984288</v>
+        <v>0.4955393371940885</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.4768513406831218</v>
+        <v>0.4846395585710421</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.4765352850573317</v>
+        <v>0.4845243155808523</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.480959373740608</v>
+        <v>0.4915092829263715</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.4799539304070355</v>
+        <v>0.4883487266684701</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.46564723775664</v>
+        <v>0.4940660211219009</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.4632057425513004</v>
+        <v>0.498116777723185</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.4850687869536654</v>
+        <v>0.5074832035066993</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.4856146384820497</v>
+        <v>0.5031129408906971</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.4826266016705403</v>
+        <v>0.5027106255417111</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.4947209049404049</v>
+        <v>0.5027106255417111</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5004085260490563</v>
+        <v>0.5041183842242698</v>
       </c>
     </row>
     <row r="126">
@@ -1680,217 +1680,217 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.4996321885402922</v>
+        <v>0.5034862729726894</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.4959540739432149</v>
+        <v>0.5092608438823224</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4919012471085741</v>
+        <v>0.5057269555424287</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4908951136972159</v>
+        <v>0.5269047527037247</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5007197511303474</v>
+        <v>0.5269047527037247</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5001738996019631</v>
+        <v>0.5268184929805287</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5014381221051237</v>
+        <v>0.5227380630344652</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5022137695361021</v>
+        <v>0.5213027012404838</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5011220664793335</v>
+        <v>0.5128030131556429</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5011220664793335</v>
+        <v>0.5128030131556429</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5011220664793335</v>
+        <v>0.5124869575298527</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5011220664793335</v>
+        <v>0.508809533010561</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.499426545360193</v>
+        <v>0.5052142277477517</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.499426545360193</v>
+        <v>0.505846338999332</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5006045081401576</v>
+        <v>0.5056758897862967</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4942833956243548</v>
+        <v>0.5036367099299434</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4948575403419473</v>
+        <v>0.4910503811989687</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4972707423580786</v>
+        <v>0.4942675238352867</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4972707423580786</v>
+        <v>0.5004395795494068</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4975867979838687</v>
+        <v>0.5038837577771766</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.4988510204870293</v>
+        <v>0.5038837577771766</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4991670761128195</v>
+        <v>0.5015568154842414</v>
       </c>
     </row>
     <row r="148">
@@ -1900,53 +1900,53 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4938810802753686</v>
+        <v>0.501501609261396</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.4924733215928099</v>
+        <v>0.5045144888731857</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5001725194463921</v>
+        <v>0.5135634788753388</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5004023153489862</v>
+        <v>0.5067820844765621</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.500086259723196</v>
+        <v>0.505775951065204</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -1956,31 +1956,31 @@
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5003160556257902</v>
+        <v>0.4997702040974059</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5003160556257902</v>
+        <v>0.4997702040974059</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5003160556257902</v>
+        <v>0.4997702040974059</v>
       </c>
     </row>
   </sheetData>
